--- a/erp-server/erp-server-file/src/main/resources/excel/scm/purchasePrice.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/scm/purchasePrice.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="采购价目数据" sheetId="1" r:id="rId1"/>
@@ -27,11 +27,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>单据编号</t>
   </si>
   <si>
+    <t>外部平台单号</t>
+  </si>
+  <si>
     <t>供应商名称</t>
   </si>
   <si>
@@ -78,6 +81,9 @@
   </si>
   <si>
     <t>{.code}</t>
+  </si>
+  <si>
+    <t>{.outPlatformCode}</t>
   </si>
   <si>
     <t>{.supplierName}</t>
@@ -135,7 +141,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -148,13 +154,6 @@
       <sz val="13"/>
       <name val="宋体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -631,151 +630,151 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -786,7 +785,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1322,20 +1321,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="2" width="30" customWidth="1"/>
-    <col min="3" max="5" width="20" customWidth="1"/>
-    <col min="6" max="7" width="10" customWidth="1"/>
-    <col min="8" max="9" width="20" customWidth="1"/>
-    <col min="10" max="10" width="10" customWidth="1"/>
-    <col min="11" max="14" width="20" customWidth="1"/>
-    <col min="15" max="15" width="10" customWidth="1"/>
-    <col min="16" max="16" width="20" customWidth="1"/>
+    <col min="1" max="3" width="30" customWidth="1"/>
+    <col min="4" max="6" width="20" customWidth="1"/>
+    <col min="7" max="8" width="10" customWidth="1"/>
+    <col min="9" max="10" width="20" customWidth="1"/>
+    <col min="11" max="11" width="10" customWidth="1"/>
+    <col min="12" max="15" width="20" customWidth="1"/>
+    <col min="16" max="16" width="10" customWidth="1"/>
+    <col min="17" max="17" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" spans="1:16">
+    <row r="1" ht="15" spans="1:17">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1384,55 +1383,61 @@
       <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:17">
       <c r="A2" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>

--- a/erp-server/erp-server-file/src/main/resources/excel/scm/purchasePrice.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/scm/purchasePrice.xlsx
@@ -83,7 +83,7 @@
     <t>{.code}</t>
   </si>
   <si>
-    <t>{.outPlatformCode}</t>
+    <t>{.voucherNo}</t>
   </si>
   <si>
     <t>{.supplierName}</t>

--- a/erp-server/erp-server-file/src/main/resources/excel/scm/purchasePrice.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/scm/purchasePrice.xlsx
@@ -32,7 +32,7 @@
     <t>单据编号</t>
   </si>
   <si>
-    <t>外部平台单号</t>
+    <t>外部平台编号</t>
   </si>
   <si>
     <t>供应商名称</t>

--- a/erp-server/erp-server-file/src/main/resources/excel/scm/purchasePrice.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/scm/purchasePrice.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="采购价目数据" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t>单据编号</t>
   </si>
@@ -38,6 +38,9 @@
     <t>供应商名称</t>
   </si>
   <si>
+    <t>是否含税</t>
+  </si>
+  <si>
     <t>SKU</t>
   </si>
   <si>
@@ -87,6 +90,9 @@
   </si>
   <si>
     <t>{.supplierName}</t>
+  </si>
+  <si>
+    <t>{.isTaxIncludedName}</t>
   </si>
   <si>
     <t>{.skuNo}</t>
@@ -1321,20 +1327,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="3" width="30" customWidth="1"/>
-    <col min="4" max="6" width="20" customWidth="1"/>
-    <col min="7" max="8" width="10" customWidth="1"/>
-    <col min="9" max="10" width="20" customWidth="1"/>
-    <col min="11" max="11" width="10" customWidth="1"/>
-    <col min="12" max="15" width="20" customWidth="1"/>
-    <col min="16" max="16" width="10" customWidth="1"/>
-    <col min="17" max="17" width="20" customWidth="1"/>
+    <col min="4" max="7" width="20" customWidth="1"/>
+    <col min="8" max="9" width="10" customWidth="1"/>
+    <col min="10" max="11" width="20" customWidth="1"/>
+    <col min="12" max="12" width="10" customWidth="1"/>
+    <col min="13" max="16" width="20" customWidth="1"/>
+    <col min="17" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" spans="1:17">
+    <row r="1" ht="15" spans="1:18">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1386,58 +1392,64 @@
       <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:18">
       <c r="A2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
